--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-05</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200119.4.101.6</t>
+    <t>http://medis.or.jp/CodeSystem/master-disease-exCode</t>
   </si>
 </sst>
 </file>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionDiseaseCodeMEDISExchange_VS</t>
+    <t>http://medis.or.jp/ValueSet/master-disease-exCode</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_ConditionDiseaseCodeMEDISExchange_VS</t>
+    <t>JP_Disease_MEDIS_Concept_VS</t>
   </si>
   <si>
     <t>Title</t>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-code-medis-exchange-vs.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MEDIS ICD10対応標準病名マスター(交換用コード) を示す値セット</t>
+    <t>MEDIS ICD10対応標準病名マスター(交換用コード) を示す値セットMEDI S病名交換用コード</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright © MEDIS-DC and MHLW and JAMI. All Rights Reserved</t>
   </si>
   <si>
     <t>Immutable</t>
